--- a/hall/resources/sample/DailyRecharge.xlsx
+++ b/hall/resources/sample/DailyRecharge.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRecharge" sheetId="1" r:id="rId1"/>
@@ -270,9 +275,8 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -895,14 +899,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1455,328 +1462,328 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
-    <col min="4" max="4" width="59.625" customWidth="1"/>
-    <col min="5" max="5" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="1" max="2" width="7" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="3" customWidth="1"/>
+    <col min="8" max="9" width="25" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:9">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:9">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:9">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+    <row r="4" s="1" customFormat="1" spans="1:9">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>1</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>57013</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>999</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>1</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="11">
         <v>1.99</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="11">
         <v>200</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>57013</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>999</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="11">
         <v>3.99</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="11">
         <v>300</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>1</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>57013</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>999</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <v>1</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="11">
         <v>7.99</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="11">
         <v>500</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>1</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>57013</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>999</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <v>1</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <v>9.99</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="11">
         <v>800</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>101</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>57013</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>102</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>57013</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>103</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>57013</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>3000</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>104</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>57013</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>105</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>57013</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>5000</v>
       </c>
     </row>
